--- a/data/trans_orig/P5710-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5710-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2007</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>392648</t>
+          <t>390054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>442042</t>
+          <t>441304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>322273</t>
+          <t>320647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>373014</t>
+          <t>375463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>728616</t>
+          <t>729921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>805133</t>
+          <t>802823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154752</t>
+          <t>153620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>197882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174687</t>
+          <t>175177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219273</t>
+          <t>222989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340192</t>
+          <t>339174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>406743</t>
+          <t>404809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>68176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104146</t>
+          <t>103142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82595</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>121303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>162214</t>
+          <t>164069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>214979</t>
+          <t>211568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49467</t>
+          <t>49202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37392</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>534871</t>
+          <t>530978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>600045</t>
+          <t>599281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>506694</t>
+          <t>509569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>573853</t>
+          <t>576138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1061054</t>
+          <t>1057935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1145386</t>
+          <t>1147898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225726</t>
+          <t>225910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283310</t>
+          <t>285772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235053</t>
+          <t>236624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295282</t>
+          <t>294131</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>485902</t>
+          <t>482102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563397</t>
+          <t>565038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93039</t>
+          <t>93245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>133545</t>
+          <t>135168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106444</t>
+          <t>107769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149525</t>
+          <t>151050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>214007</t>
+          <t>210054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>274400</t>
+          <t>269919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>45521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68076</t>
+          <t>69377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>387329</t>
+          <t>386564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>437734</t>
+          <t>437536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>361456</t>
+          <t>362249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413910</t>
+          <t>411353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>759530</t>
+          <t>766702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>836247</t>
+          <t>838289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137420</t>
+          <t>137355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179643</t>
+          <t>183806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,49 +2225,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>159165</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>138032</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>181111</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>20,18%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>26,48%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>159165</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>139441</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>181251</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>317</t>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287028</t>
+          <t>286287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353607</t>
+          <t>349189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73300</t>
+          <t>73693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111489</t>
+          <t>109247</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119477</t>
+          <t>118256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167719</t>
+          <t>169738</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>217745</t>
+          <t>222157</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43718</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33235</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>60333</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,77 +2569,77 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3669</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3669</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>7341</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>15112</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>7341</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>3079</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>16165</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>516212</t>
+          <t>519981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>578261</t>
+          <t>578727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573684</t>
+          <t>573369</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>635442</t>
+          <t>638631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1106683</t>
+          <t>1111214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1196268</t>
+          <t>1195977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232566</t>
+          <t>231877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>285008</t>
+          <t>286547</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>231233</t>
+          <t>228142</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>288698</t>
+          <t>284294</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477595</t>
+          <t>477516</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>554015</t>
+          <t>553859</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77130</t>
+          <t>75211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113686</t>
+          <t>111736</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101114</t>
+          <t>100220</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>140341</t>
+          <t>140307</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>184634</t>
+          <t>188453</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239061</t>
+          <t>243068</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55010</t>
+          <t>54080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>36662</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>65516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73644</t>
+          <t>73312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112896</t>
+          <t>109717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1886294</t>
+          <t>1888168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1997171</t>
+          <t>2002761</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1818350</t>
+          <t>1822965</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1941078</t>
+          <t>1938194</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3743118</t>
+          <t>3749121</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3910400</t>
+          <t>3905908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,69%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>801419</t>
+          <t>794750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>903240</t>
+          <t>897216</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>827125</t>
+          <t>824157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>939668</t>
+          <t>932696</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1654045</t>
+          <t>1652903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1798798</t>
+          <t>1795860</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>346828</t>
+          <t>345182</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>422984</t>
+          <t>422155</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>411818</t>
+          <t>410181</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>493697</t>
+          <t>491404</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>778533</t>
+          <t>778975</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>887055</t>
+          <t>883565</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>71732</t>
+          <t>70467</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>111882</t>
+          <t>111053</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>126572</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>173427</t>
+          <t>177074</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>205874</t>
+          <t>208490</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>270007</t>
+          <t>271605</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18615</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>44058</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2012</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>418590</t>
+          <t>419410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>474214</t>
+          <t>470595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397971</t>
+          <t>397690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>453927</t>
+          <t>449948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>834969</t>
+          <t>836304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>909550</t>
+          <t>907693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159684</t>
+          <t>162129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206667</t>
+          <t>210405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174403</t>
+          <t>175211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223900</t>
+          <t>224805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343829</t>
+          <t>349881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>416337</t>
+          <t>414755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40746</t>
+          <t>40197</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63119</t>
+          <t>62331</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82477</t>
+          <t>81839</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121256</t>
+          <t>120415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>22997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>44972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>562815</t>
+          <t>563000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>628927</t>
+          <t>629640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>548091</t>
+          <t>549967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>614253</t>
+          <t>614410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1133025</t>
+          <t>1136129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1225884</t>
+          <t>1231137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267535</t>
+          <t>267181</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327856</t>
+          <t>329156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287811</t>
+          <t>285174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348064</t>
+          <t>345516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>571134</t>
+          <t>567751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656658</t>
+          <t>655937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76705</t>
+          <t>74444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114143</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84022</t>
+          <t>86525</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125096</t>
+          <t>128309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>170509</t>
+          <t>170043</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225231</t>
+          <t>226040</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>37250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>35031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31871</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60931</t>
+          <t>62048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>445898</t>
+          <t>447748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>501868</t>
+          <t>505635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>428791</t>
+          <t>431607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>488733</t>
+          <t>485650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>894562</t>
+          <t>891498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>971363</t>
+          <t>972582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160725</t>
+          <t>155842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210291</t>
+          <t>206255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175165</t>
+          <t>178081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>227799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351389</t>
+          <t>346798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418558</t>
+          <t>416040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>55915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91783</t>
+          <t>92010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66984</t>
+          <t>66326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104071</t>
+          <t>105019</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134926</t>
+          <t>133659</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>185469</t>
+          <t>183660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30470</t>
+          <t>30310</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27587</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54459</t>
+          <t>54497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>20163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>494926</t>
+          <t>494821</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>558568</t>
+          <t>557878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>533772</t>
+          <t>533260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>595781</t>
+          <t>598325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1049915</t>
+          <t>1049609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1139025</t>
+          <t>1136588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243481</t>
+          <t>246992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>301638</t>
+          <t>305379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>290166</t>
+          <t>293002</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351637</t>
+          <t>351556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>554862</t>
+          <t>554406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638640</t>
+          <t>636834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97666</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142477</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109471</t>
+          <t>110524</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154598</t>
+          <t>155602</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>219709</t>
+          <t>219732</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>281644</t>
+          <t>280318</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>32157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29344</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>27385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1989741</t>
+          <t>1988240</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2106816</t>
+          <t>2111074</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1963314</t>
+          <t>1971812</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2087487</t>
+          <t>2094317</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3991843</t>
+          <t>3998426</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4160494</t>
+          <t>4162132</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>881510</t>
+          <t>882563</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>989734</t>
+          <t>992388</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>984629</t>
+          <t>986836</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1095766</t>
+          <t>1095181</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1896682</t>
+          <t>1899999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2055079</t>
+          <t>2050299</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>305576</t>
+          <t>303436</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>378047</t>
+          <t>376462</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>333627</t>
+          <t>334013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>406913</t>
+          <t>407745</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>657339</t>
+          <t>655900</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>761470</t>
+          <t>760502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61689</t>
+          <t>60978</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>98499</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>61818</t>
+          <t>59903</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>97082</t>
+          <t>95413</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>132547</t>
+          <t>130815</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>183628</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>24366</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49717</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>66157</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2016</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>300180</t>
+          <t>304605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353683</t>
+          <t>356097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>289004</t>
+          <t>291644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>340433</t>
+          <t>344681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>608279</t>
+          <t>604020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>683537</t>
+          <t>677463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213580</t>
+          <t>212263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263060</t>
+          <t>261943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210967</t>
+          <t>206835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258857</t>
+          <t>256199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>437739</t>
+          <t>438127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506752</t>
+          <t>506532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64698</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101230</t>
+          <t>99423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81085</t>
+          <t>80278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119314</t>
+          <t>118162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>155772</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>203146</t>
+          <t>204486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>35778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59169</t>
+          <t>57283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>502647</t>
+          <t>505063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>568985</t>
+          <t>567497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>526681</t>
+          <t>529821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>595419</t>
+          <t>598548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1053865</t>
+          <t>1050730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1152245</t>
+          <t>1144418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312622</t>
+          <t>311779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>378133</t>
+          <t>373911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330666</t>
+          <t>330912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>398512</t>
+          <t>395400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655970</t>
+          <t>659873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>749716</t>
+          <t>746636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96246</t>
+          <t>97249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142030</t>
+          <t>141044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>79386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118914</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>186635</t>
+          <t>188972</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>246365</t>
+          <t>247046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>49924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>267711</t>
+          <t>269842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>324466</t>
+          <t>326996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293198</t>
+          <t>294801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>350299</t>
+          <t>350616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>583130</t>
+          <t>576206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>659982</t>
+          <t>659577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>293457</t>
+          <t>291609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347066</t>
+          <t>349654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>288305</t>
+          <t>289489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348411</t>
+          <t>345556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>598458</t>
+          <t>597750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>676014</t>
+          <t>680703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106407</t>
+          <t>102670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147241</t>
+          <t>144884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107620</t>
+          <t>109157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150304</t>
+          <t>148595</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>226834</t>
+          <t>221625</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283580</t>
+          <t>283306</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>38068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>463337</t>
+          <t>461691</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>524682</t>
+          <t>521037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>530251</t>
+          <t>530293</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>596775</t>
+          <t>600102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1007730</t>
+          <t>1013907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1099216</t>
+          <t>1103814</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>276086</t>
+          <t>276504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>331095</t>
+          <t>329983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288872</t>
+          <t>286862</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352073</t>
+          <t>349758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>581953</t>
+          <t>580426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>665137</t>
+          <t>663503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95137</t>
+          <t>92471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134009</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101476</t>
+          <t>101329</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>146281</t>
+          <t>142574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>207529</t>
+          <t>204134</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>267355</t>
+          <t>264794</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65571</t>
+          <t>63657</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>18846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1591646</t>
+          <t>1588154</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1707165</t>
+          <t>1706897</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1705535</t>
+          <t>1701340</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1829180</t>
+          <t>1829509</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3329198</t>
+          <t>3329239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3499847</t>
+          <t>3505781</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1147245</t>
+          <t>1147132</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1261567</t>
+          <t>1264616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1166480</t>
+          <t>1175572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1289680</t>
+          <t>1286362</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2354441</t>
+          <t>2350594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2516411</t>
+          <t>2517720</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>397396</t>
+          <t>396961</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>475902</t>
+          <t>479442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>400788</t>
+          <t>404747</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>486376</t>
+          <t>487619</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>827069</t>
+          <t>825782</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>939590</t>
+          <t>937804</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>101091</t>
+          <t>100859</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>57574</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>91983</t>
+          <t>93538</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>130857</t>
+          <t>128527</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>181552</t>
+          <t>178852</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>53692</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2023</t>
+          <t>Población según la frecuencia de recibir consejos útiles cuando me ocurre algún acontecimiento importante en mi vida en 2023 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>320208</t>
+          <t>319264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>375575</t>
+          <t>374367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>336636</t>
+          <t>337840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>377117</t>
+          <t>380515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668506</t>
+          <t>671083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>741274</t>
+          <t>737991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162694</t>
+          <t>165534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210426</t>
+          <t>209780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193951</t>
+          <t>192629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229823</t>
+          <t>232061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367259</t>
+          <t>368287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>428841</t>
+          <t>427807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50160</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>80922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58840</t>
+          <t>58946</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82765</t>
+          <t>82181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113835</t>
+          <t>115118</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151536</t>
+          <t>151623</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>40469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41529</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65070</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>25277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>590477</t>
+          <t>583099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>936995</t>
+          <t>973240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>450712</t>
+          <t>450498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>504343</t>
+          <t>503117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1061474</t>
+          <t>1066000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1511122</t>
+          <t>1520070</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187116</t>
+          <t>171013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448653</t>
+          <t>455294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310029</t>
+          <t>311575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361457</t>
+          <t>360050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>450626</t>
+          <t>465386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>787343</t>
+          <t>780706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40289</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103068</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77312</t>
+          <t>76690</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103482</t>
+          <t>104249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>106297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194561</t>
+          <t>196608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>42289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>30528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53109</t>
+          <t>53662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44661</t>
+          <t>44511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84781</t>
+          <t>85768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66906</t>
+          <t>74150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>338516</t>
+          <t>340242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>401378</t>
+          <t>400314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>212804</t>
+          <t>215888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>532468</t>
+          <t>533821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,17 +13088,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>773951</t>
+          <t>773950</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>489416</t>
+          <t>482660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>903249</t>
+          <t>904795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221365</t>
+          <t>221757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282489</t>
+          <t>280006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122949</t>
+          <t>115629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>305189</t>
+          <t>302979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>281873</t>
+          <t>297493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>563294</t>
+          <t>558363</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49899</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84888</t>
+          <t>84519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>37290</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>102761</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87369</t>
+          <t>89250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>170995</t>
+          <t>171697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>557522</t>
+          <t>562816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>33034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>771932</t>
+          <t>768471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>508968</t>
+          <t>510173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571012</t>
+          <t>574084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>642116</t>
+          <t>643760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>769043</t>
+          <t>765316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1172148</t>
+          <t>1171532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1322303</t>
+          <t>1314813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234042</t>
+          <t>232776</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291236</t>
+          <t>290404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>218638</t>
+          <t>217952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>308472</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>472064</t>
+          <t>477628</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582865</t>
+          <t>582194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63991</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96821</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62383</t>
+          <t>62922</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95711</t>
+          <t>97560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>132303</t>
+          <t>133616</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>180514</t>
+          <t>184531</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>24794</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45173</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50808</t>
+          <t>50744</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59812</t>
+          <t>59641</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88776</t>
+          <t>88954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1841550</t>
+          <t>1845985</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2284018</t>
+          <t>2336119</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1611141</t>
+          <t>1530051</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2074514</t>
+          <t>2063551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3582663</t>
+          <t>3581102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4239112</t>
+          <t>4237330</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>822954</t>
+          <t>803883</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1146715</t>
+          <t>1143853</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>873202</t>
+          <t>867294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1136265</t>
+          <t>1139617</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1818994</t>
+          <t>1732198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2253177</t>
+          <t>2237865</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>224413</t>
+          <t>224734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>324961</t>
+          <t>322050</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>251946</t>
+          <t>255259</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>345674</t>
+          <t>345877</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>512674</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>651291</t>
+          <t>652616</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>79042</t>
+          <t>79331</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>127686</t>
+          <t>127661</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>119347</t>
+          <t>120893</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>949440</t>
+          <t>946725</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>222807</t>
+          <t>220443</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1117526</t>
+          <t>1168160</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>24316</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75926</t>
+          <t>73637</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,47 +14854,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>37503</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>26934</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>49883</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>37503</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>27603</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>51074</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59802</t>
+          <t>61046</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112000</t>
+          <t>117155</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5710-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5710-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>390054</t>
+          <t>388268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>441304</t>
+          <t>441307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>320647</t>
+          <t>324904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>375463</t>
+          <t>374918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>729921</t>
+          <t>728676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>802823</t>
+          <t>801882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153620</t>
+          <t>153614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197882</t>
+          <t>198877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,47 +861,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>28,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>196262</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>173093</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>218199</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>28,51%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>196262</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>175177</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>222989</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>339174</t>
+          <t>340074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>404809</t>
+          <t>404764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>70253</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103142</t>
+          <t>104677</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83025</t>
+          <t>84181</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121303</t>
+          <t>122845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>164069</t>
+          <t>162526</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>211568</t>
+          <t>213630</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49202</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>66699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>530978</t>
+          <t>533155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>599281</t>
+          <t>596162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>509569</t>
+          <t>507116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>576138</t>
+          <t>571410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1057935</t>
+          <t>1059890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1147898</t>
+          <t>1154343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225910</t>
+          <t>228412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285772</t>
+          <t>282256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236624</t>
+          <t>239209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>294131</t>
+          <t>295722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>482102</t>
+          <t>481086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>565038</t>
+          <t>562384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93245</t>
+          <t>93988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135168</t>
+          <t>135533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107769</t>
+          <t>105107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151050</t>
+          <t>149393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210054</t>
+          <t>209246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269919</t>
+          <t>269962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45521</t>
+          <t>44903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69377</t>
+          <t>69040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>386564</t>
+          <t>386006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>437536</t>
+          <t>438079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>362249</t>
+          <t>364715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>411353</t>
+          <t>412602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>766702</t>
+          <t>761939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>838289</t>
+          <t>835009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137355</t>
+          <t>135588</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183806</t>
+          <t>180442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138032</t>
+          <t>139113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181111</t>
+          <t>181954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286287</t>
+          <t>287579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349189</t>
+          <t>346293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73693</t>
+          <t>72756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>108807</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>82965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118256</t>
+          <t>119555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169738</t>
+          <t>166103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>222157</t>
+          <t>221247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>519981</t>
+          <t>514484</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>578727</t>
+          <t>576837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>573369</t>
+          <t>571433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>638631</t>
+          <t>635382</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1111214</t>
+          <t>1110115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1195977</t>
+          <t>1194246</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231877</t>
+          <t>232408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>286547</t>
+          <t>285560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228142</t>
+          <t>229639</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284294</t>
+          <t>286733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477516</t>
+          <t>477234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>553859</t>
+          <t>555628</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75211</t>
+          <t>77946</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111736</t>
+          <t>111644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100220</t>
+          <t>99964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>140307</t>
+          <t>140294</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>188453</t>
+          <t>184853</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243068</t>
+          <t>241221</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>55549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65516</t>
+          <t>65200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73312</t>
+          <t>75141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109717</t>
+          <t>113155</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1888168</t>
+          <t>1888238</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2002761</t>
+          <t>1998390</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1822965</t>
+          <t>1825180</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1938194</t>
+          <t>1937639</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3749121</t>
+          <t>3749145</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3905908</t>
+          <t>3911954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>794750</t>
+          <t>799872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>897216</t>
+          <t>900640</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>824157</t>
+          <t>829624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>932696</t>
+          <t>929376</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1652903</t>
+          <t>1655632</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1795860</t>
+          <t>1798595</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>345182</t>
+          <t>347865</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>422155</t>
+          <t>421066</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>410181</t>
+          <t>409744</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>491404</t>
+          <t>484985</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>778975</t>
+          <t>781107</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>883565</t>
+          <t>890008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>70467</t>
+          <t>72919</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>111053</t>
+          <t>110509</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>177074</t>
+          <t>175528</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>208490</t>
+          <t>211583</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>271605</t>
+          <t>271942</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>30525</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>44086</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>419410</t>
+          <t>420046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>470595</t>
+          <t>472421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397690</t>
+          <t>399001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>449948</t>
+          <t>450186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>836304</t>
+          <t>831298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>907693</t>
+          <t>906129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162129</t>
+          <t>160923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210405</t>
+          <t>209979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175211</t>
+          <t>175480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224805</t>
+          <t>225100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>349881</t>
+          <t>351198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414755</t>
+          <t>416187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40197</t>
+          <t>41410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68514</t>
+          <t>68889</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35428</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>61873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81839</t>
+          <t>81563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120415</t>
+          <t>120188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>44039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>563000</t>
+          <t>562787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>629640</t>
+          <t>627375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>549967</t>
+          <t>550716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>614410</t>
+          <t>615065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1136129</t>
+          <t>1129445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1231137</t>
+          <t>1224856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267181</t>
+          <t>267924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329156</t>
+          <t>329789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285174</t>
+          <t>286182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345516</t>
+          <t>346223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567751</t>
+          <t>568460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655937</t>
+          <t>653661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74444</t>
+          <t>76378</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86525</t>
+          <t>86708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128309</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>170043</t>
+          <t>172619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>226040</t>
+          <t>226356</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>33761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>62136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,77 +5529,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6038</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15894</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>19954</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6038</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14521</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>10204</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>5063</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>20517</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>447748</t>
+          <t>448157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>505635</t>
+          <t>502657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>431607</t>
+          <t>428154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>485650</t>
+          <t>484480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>891498</t>
+          <t>893509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>972582</t>
+          <t>972240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155842</t>
+          <t>158084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206255</t>
+          <t>207654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178081</t>
+          <t>176477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227799</t>
+          <t>228312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>346798</t>
+          <t>350736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416040</t>
+          <t>420872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55915</t>
+          <t>56581</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92010</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66326</t>
+          <t>69948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105019</t>
+          <t>106333</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133659</t>
+          <t>133583</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>183660</t>
+          <t>183609</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>54478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>494821</t>
+          <t>496034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>557878</t>
+          <t>560694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>533260</t>
+          <t>532429</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>598325</t>
+          <t>597741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1049609</t>
+          <t>1049351</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1136588</t>
+          <t>1136286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246992</t>
+          <t>247372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>305379</t>
+          <t>303384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293002</t>
+          <t>293700</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>351556</t>
+          <t>355723</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>554406</t>
+          <t>553139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>636834</t>
+          <t>634748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>99718</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>142944</t>
+          <t>143066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110524</t>
+          <t>109971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155602</t>
+          <t>155454</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>219732</t>
+          <t>218685</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>280318</t>
+          <t>281768</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>26777</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53538</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1988240</t>
+          <t>1991741</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2111074</t>
+          <t>2112712</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1971812</t>
+          <t>1964923</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2094317</t>
+          <t>2091853</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3998426</t>
+          <t>3995360</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4162132</t>
+          <t>4163155</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>882563</t>
+          <t>881067</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>992388</t>
+          <t>990491</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>986836</t>
+          <t>978005</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1095181</t>
+          <t>1095458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1899999</t>
+          <t>1894981</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2050299</t>
+          <t>2050026</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>302272</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>376462</t>
+          <t>378226</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>334013</t>
+          <t>330047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>407745</t>
+          <t>406202</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>655900</t>
+          <t>654919</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>760502</t>
+          <t>760537</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>60978</t>
+          <t>62283</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>98967</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>59903</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95413</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>130815</t>
+          <t>132788</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>183628</t>
+          <t>183256</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51639</t>
+          <t>50853</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>68709</t>
+          <t>68252</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304605</t>
+          <t>304370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>356097</t>
+          <t>356536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>291644</t>
+          <t>289217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>344681</t>
+          <t>342059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604020</t>
+          <t>602939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>677463</t>
+          <t>681541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212263</t>
+          <t>211401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261943</t>
+          <t>260792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206835</t>
+          <t>208016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256199</t>
+          <t>256850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438127</t>
+          <t>433757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506532</t>
+          <t>509096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64520</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99423</t>
+          <t>99697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80278</t>
+          <t>81673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118162</t>
+          <t>117761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155772</t>
+          <t>153993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>204486</t>
+          <t>205862</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>37052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>59637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>12252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>505063</t>
+          <t>497589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>567497</t>
+          <t>563955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>529821</t>
+          <t>534766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>598548</t>
+          <t>599320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1050730</t>
+          <t>1049116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1144418</t>
+          <t>1145326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311779</t>
+          <t>315403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>373911</t>
+          <t>377443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330912</t>
+          <t>331139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>395400</t>
+          <t>391899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659873</t>
+          <t>662197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>746636</t>
+          <t>752299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97249</t>
+          <t>96954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141044</t>
+          <t>141194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79386</t>
+          <t>79181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118147</t>
+          <t>117034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>188972</t>
+          <t>187290</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>247046</t>
+          <t>246651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49924</t>
+          <t>50192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,47 +9166,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12872</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14273</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>269842</t>
+          <t>268667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>326996</t>
+          <t>326779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294801</t>
+          <t>292697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>350616</t>
+          <t>350372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>576206</t>
+          <t>574885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>659577</t>
+          <t>656645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291609</t>
+          <t>293897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349654</t>
+          <t>351926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289489</t>
+          <t>292362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>345556</t>
+          <t>345932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>597750</t>
+          <t>598788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>680703</t>
+          <t>676018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102670</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>147405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109157</t>
+          <t>108416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148595</t>
+          <t>150753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221625</t>
+          <t>223037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283306</t>
+          <t>285050</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38068</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461691</t>
+          <t>457542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>521037</t>
+          <t>519970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>530293</t>
+          <t>533564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>600102</t>
+          <t>596714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1013907</t>
+          <t>1011358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1103814</t>
+          <t>1100154</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>276504</t>
+          <t>274427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>329983</t>
+          <t>333318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>286862</t>
+          <t>288535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349758</t>
+          <t>350086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580426</t>
+          <t>578046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>663503</t>
+          <t>664231</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92471</t>
+          <t>93304</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>133344</t>
+          <t>134393</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101329</t>
+          <t>99168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142574</t>
+          <t>143775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>204134</t>
+          <t>208437</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>264794</t>
+          <t>264487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>41996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35041</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63657</t>
+          <t>63489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1588154</t>
+          <t>1595081</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1706897</t>
+          <t>1710129</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1701340</t>
+          <t>1705466</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1829509</t>
+          <t>1825133</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3329239</t>
+          <t>3335283</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3505781</t>
+          <t>3503889</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1147132</t>
+          <t>1148006</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1264616</t>
+          <t>1262345</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1175572</t>
+          <t>1170183</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1286362</t>
+          <t>1290224</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2350594</t>
+          <t>2355295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2517720</t>
+          <t>2522926</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>396961</t>
+          <t>397150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479442</t>
+          <t>476625</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>404747</t>
+          <t>404132</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>487619</t>
+          <t>485922</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>825782</t>
+          <t>823072</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>937804</t>
+          <t>939837</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63560</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100859</t>
+          <t>99893</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>57574</t>
+          <t>56458</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>93538</t>
+          <t>91147</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>128527</t>
+          <t>130001</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>178852</t>
+          <t>179707</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,82 +11212,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>22835</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>14932</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>37313</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>39841</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>28676</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>54848</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>22835</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>15056</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>35715</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>39841</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>27663</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>53692</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>345893</t>
+          <t>369049</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>319264</t>
+          <t>342361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374367</t>
+          <t>397373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>358726</t>
+          <t>387289</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>337840</t>
+          <t>364418</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>380515</t>
+          <t>409697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>704620</t>
+          <t>756338</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>671083</t>
+          <t>724657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>737991</t>
+          <t>799648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>187187</t>
+          <t>206589</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165534</t>
+          <t>183485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209780</t>
+          <t>230400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>210499</t>
+          <t>231615</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192629</t>
+          <t>211539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232061</t>
+          <t>252498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>397686</t>
+          <t>438203</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368287</t>
+          <t>406653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427807</t>
+          <t>470402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63340</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>54724</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80922</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>73149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58946</t>
+          <t>61965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82181</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>132271</t>
+          <t>143209</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115118</t>
+          <t>121955</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151623</t>
+          <t>162823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40469</t>
+          <t>46192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>29472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>56598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64630</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>634642</t>
+          <t>689896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>669139</t>
+          <t>726369</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>669139</t>
+          <t>726369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>669139</t>
+          <t>726369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1303781</t>
+          <t>1416265</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1303781</t>
+          <t>1416265</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1303781</t>
+          <t>1416265</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>722762</t>
+          <t>527087</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>583099</t>
+          <t>488349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>973240</t>
+          <t>559233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>477785</t>
+          <t>523201</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>450498</t>
+          <t>492612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>503117</t>
+          <t>550619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1200546</t>
+          <t>1050289</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1066000</t>
+          <t>1005193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1520070</t>
+          <t>1098819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>348098</t>
+          <t>387760</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171013</t>
+          <t>355621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455294</t>
+          <t>422618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>334376</t>
+          <t>382502</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311575</t>
+          <t>355891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>360050</t>
+          <t>411404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>682474</t>
+          <t>770262</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465386</t>
+          <t>724896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>780706</t>
+          <t>813684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74902</t>
+          <t>85975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38876</t>
+          <t>68350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103814</t>
+          <t>105175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,17 +12597,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>100199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76690</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104249</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>164476</t>
+          <t>186173</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106297</t>
+          <t>161918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>196608</t>
+          <t>212854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>7,66%</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>34826</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>47551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,27 +12710,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40253</t>
+          <t>46106</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>35691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>59915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>80932</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>64298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85768</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54470</t>
+          <t>21462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,67 +12823,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>27393</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>18180</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>41510</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>31810</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>17903</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>74150</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192181</t>
+          <t>1048182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192181</t>
+          <t>1048182</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192181</t>
+          <t>1048182</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>954378</t>
+          <t>1066866</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>954378</t>
+          <t>1066866</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>954378</t>
+          <t>1066866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2146558</t>
+          <t>2115049</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2146558</t>
+          <t>2115049</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2146558</t>
+          <t>2115049</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,69 +13018,69 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>370067</t>
+          <t>418974</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>340242</t>
+          <t>385888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>400314</t>
+          <t>452968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>56,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>435503</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>409900</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>461769</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>53,74%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>56,99%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>403884</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>215888</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>533821</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>896</t>
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>773950</t>
+          <t>854477</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>482660</t>
+          <t>810546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>904795</t>
+          <t>894371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,55%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>249754</t>
+          <t>278577</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>221757</t>
+          <t>248125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280006</t>
+          <t>311631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>226174</t>
+          <t>258242</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115629</t>
+          <t>233350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>302979</t>
+          <t>284832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>475928</t>
+          <t>536819</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297493</t>
+          <t>499666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558363</t>
+          <t>576346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>78809</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50487</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84519</t>
+          <t>103256</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>89397</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37290</t>
+          <t>72607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102761</t>
+          <t>107677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>138329</t>
+          <t>168206</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89250</t>
+          <t>144393</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171697</t>
+          <t>198672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>222593</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>562816</t>
+          <t>29629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>236966</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>768471</t>
+          <t>53523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>702378</t>
+          <t>799762</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>702378</t>
+          <t>799762</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>702378</t>
+          <t>799762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>931462</t>
+          <t>810333</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>931462</t>
+          <t>810333</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>931462</t>
+          <t>810333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1633840</t>
+          <t>1610095</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1633840</t>
+          <t>1610095</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1633840</t>
+          <t>1610095</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>539962</t>
+          <t>566663</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>510173</t>
+          <t>533521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574084</t>
+          <t>597266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>680374</t>
+          <t>651891</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>643760</t>
+          <t>625571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>765316</t>
+          <t>682337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1220337</t>
+          <t>1218554</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1171532</t>
+          <t>1174181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1314813</t>
+          <t>1260344</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>262690</t>
+          <t>286501</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232776</t>
+          <t>257106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>290404</t>
+          <t>313727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>277482</t>
+          <t>312487</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>285618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306157</t>
+          <t>339473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>540172</t>
+          <t>598988</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>477628</t>
+          <t>555640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582194</t>
+          <t>636345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79606</t>
+          <t>87090</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96302</t>
+          <t>104727</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>80365</t>
+          <t>87293</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>73633</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97560</t>
+          <t>104081</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>159971</t>
+          <t>174383</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>133616</t>
+          <t>150188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>184531</t>
+          <t>198198</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33722</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>27776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>49933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>39895</t>
+          <t>46786</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29657</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50744</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>73617</t>
+          <t>83904</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59641</t>
+          <t>69742</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88954</t>
+          <t>102112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>19443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>23584</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>924562</t>
+          <t>987730</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>924562</t>
+          <t>987730</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>924562</t>
+          <t>987730</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1088321</t>
+          <t>1111683</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1088321</t>
+          <t>1111683</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1088321</t>
+          <t>1111683</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2012883</t>
+          <t>2099413</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2012883</t>
+          <t>2099413</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2012883</t>
+          <t>2099413</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1978684</t>
+          <t>1881773</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1845985</t>
+          <t>1825200</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2336119</t>
+          <t>1946967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1920770</t>
+          <t>1997884</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1530051</t>
+          <t>1940692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2063551</t>
+          <t>2047442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3899453</t>
+          <t>3879658</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3581102</t>
+          <t>3789237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4237330</t>
+          <t>3960431</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1047729</t>
+          <t>1159427</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>803883</t>
+          <t>1100008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1143853</t>
+          <t>1218158</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1048532</t>
+          <t>1184846</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>867294</t>
+          <t>1138251</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1139617</t>
+          <t>1239086</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2096260</t>
+          <t>2344273</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1732198</t>
+          <t>2251349</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2237865</t>
+          <t>2417863</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>283041</t>
+          <t>321933</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>224734</t>
+          <t>285327</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>322050</t>
+          <t>359627</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>312006</t>
+          <t>350038</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>255259</t>
+          <t>319202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>345877</t>
+          <t>380008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>595047</t>
+          <t>671972</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>512674</t>
+          <t>625334</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>652616</t>
+          <t>723605</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>124770</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>79331</t>
+          <t>106958</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>127661</t>
+          <t>147684</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>324490</t>
+          <t>136305</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>120893</t>
+          <t>118667</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>946725</t>
+          <t>157120</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>429497</t>
+          <t>261075</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>220443</t>
+          <t>234647</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1168160</t>
+          <t>287474</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>39301</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>73637</t>
+          <t>51081</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26934</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49883</t>
+          <t>62157</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>76804</t>
+          <t>83845</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61046</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>117155</t>
+          <t>103412</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3453762</t>
+          <t>3525570</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3453762</t>
+          <t>3525570</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3453762</t>
+          <t>3525570</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3643300</t>
+          <t>3715252</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3643300</t>
+          <t>3715252</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3643300</t>
+          <t>3715252</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7097062</t>
+          <t>7240822</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7097062</t>
+          <t>7240822</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7097062</t>
+          <t>7240822</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
